--- a/output/pdf_financials_xlsx/METL.xlsx
+++ b/output/pdf_financials_xlsx/METL.xlsx
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.913292</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.662187</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3210,7 +3210,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3881,7 +3885,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.913292</v>
       </c>
@@ -7288,7 +7296,7 @@
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.005033</v>
+        <v>-0.005033</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7354,7 +7362,7 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.005033</v>
+        <v>-0.005033</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/METL.xlsx
+++ b/output/pdf_financials_xlsx/METL.xlsx
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.013399</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.011385</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017906</v>
       </c>
     </row>
     <row r="35">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.013399</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.011385</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017906</v>
       </c>
     </row>
     <row r="37">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.030361</v>
+        <v>0.016962</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.022801</v>
+        <v>0.011416</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.017906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">

--- a/output/pdf_financials_xlsx/METL.xlsx
+++ b/output/pdf_financials_xlsx/METL.xlsx
@@ -927,7 +927,7 @@
         <v>0.014338</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.014338</v>
       </c>
     </row>
     <row r="29">
@@ -945,7 +945,7 @@
         <v>-0.276925</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.393059</v>
+        <v>-0.378721</v>
       </c>
     </row>
     <row r="30">
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.014338</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.014338</v>
       </c>
     </row>
     <row r="101">
@@ -4112,7 +4112,11 @@
           <t>Depreciation of right-of-use assets 5</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -6288,17 +6292,21 @@
           <t>Depreciation of right-of-use assets 5</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.014338</v>
+        <v>0.014338</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>-0.014338</v>
+        <v>0.014338</v>
       </c>
     </row>
     <row r="116">

--- a/output/pdf_financials_xlsx/METL.xlsx
+++ b/output/pdf_financials_xlsx/METL.xlsx
@@ -1609,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.035182</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.022659</v>
       </c>
     </row>
     <row r="71">
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.035182</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.022659</v>
       </c>
     </row>
     <row r="72">
@@ -1689,10 +1689,10 @@
         <v>0.245182</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.245525</v>
+        <v>0.210343</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.357861</v>
+        <v>0.335202</v>
       </c>
     </row>
     <row r="76">
@@ -1770,15 +1770,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>-0.05631805244740692</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.0259226039981604</v>
       </c>
     </row>
     <row r="81">
@@ -2993,7 +2989,11 @@
           <t>Current portion of lease obligations 6</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3115,7 +3115,11 @@
           <t>Lease obligations 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
